--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22785" windowHeight="8460"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,7 +14,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+  <x:si>
+    <x:t>칼 공격 2번째</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2D/skill_Sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Tree_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼 공격1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼 공격2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼 공격 1번째</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Sword_02</x:t>
+  </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
@@ -22,58 +76,31 @@
     <x:t>2D/tree-2</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>SpritePath</x:t>
   </x:si>
   <x:si>
     <x:t>나무</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
   </x:si>
   <x:si>
     <x:t>skill_fireball_01</x:t>
   </x:si>
   <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
   </x:si>
   <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_rest_coffee_01</x:t>
   </x:si>
   <x:si>
     <x:t>skill_normalSword_01</x:t>
   </x:si>
   <x:si>
-    <x:t>SpritePath</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_Tree_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Sword_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -247,7 +274,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -283,6 +310,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -948,59 +981,59 @@
     <x:col min="1" max="1" width="23" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <x:col min="4" max="4" width="21" customWidth="1"/>
+    <x:col min="4" max="4" width="21" style="13" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F3" s="2"/>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="3"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D4" s="12"/>
       <x:c r="E4" s="3"/>
       <x:c r="F4" s="3"/>
       <x:c r="G4" s="3"/>
@@ -1015,15 +1048,15 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="3"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D5" s="12"/>
       <x:c r="E5" s="3"/>
       <x:c r="F5" s="3"/>
       <x:c r="G5" s="3"/>
@@ -1038,15 +1071,15 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="3"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="12"/>
       <x:c r="E6" s="3"/>
       <x:c r="F6" s="3"/>
       <x:c r="G6" s="3"/>
@@ -1061,17 +1094,19 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="3"/>
       <x:c r="G7" s="3"/>
@@ -1085,11 +1120,21 @@
       <x:c r="O7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3"/>
+      <x:c r="A8" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="F8" s="3"/>
       <x:c r="G8" s="3"/>
       <x:c r="H8" s="3"/>
@@ -1102,10 +1147,16 @@
       <x:c r="O8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="3"/>
+      <x:c r="A9" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="12"/>
       <x:c r="E9" s="3"/>
       <x:c r="F9" s="3"/>
       <x:c r="G9" s="3"/>
@@ -1122,7 +1173,7 @@
       <x:c r="A10" s="7"/>
       <x:c r="B10" s="7"/>
       <x:c r="C10" s="7"/>
-      <x:c r="D10" s="3"/>
+      <x:c r="D10" s="12"/>
       <x:c r="E10" s="3"/>
       <x:c r="F10" s="3"/>
       <x:c r="G10" s="3"/>
@@ -1139,7 +1190,7 @@
       <x:c r="A11" s="7"/>
       <x:c r="B11" s="7"/>
       <x:c r="C11" s="7"/>
-      <x:c r="D11" s="3"/>
+      <x:c r="D11" s="12"/>
       <x:c r="E11" s="3"/>
       <x:c r="F11" s="3"/>
       <x:c r="G11" s="3"/>
@@ -1156,7 +1207,7 @@
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>
       <x:c r="C12" s="6"/>
-      <x:c r="D12" s="3"/>
+      <x:c r="D12" s="12"/>
       <x:c r="E12" s="3"/>
       <x:c r="F12" s="3"/>
       <x:c r="G12" s="3"/>
@@ -1173,7 +1224,7 @@
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
-      <x:c r="D13" s="3"/>
+      <x:c r="D13" s="12"/>
       <x:c r="E13" s="3"/>
       <x:c r="F13" s="3"/>
       <x:c r="G13" s="3"/>
@@ -1190,7 +1241,7 @@
       <x:c r="A14" s="7"/>
       <x:c r="B14" s="7"/>
       <x:c r="C14" s="7"/>
-      <x:c r="D14" s="3"/>
+      <x:c r="D14" s="12"/>
       <x:c r="E14" s="3"/>
       <x:c r="F14" s="3"/>
       <x:c r="G14" s="3"/>
@@ -1207,7 +1258,7 @@
       <x:c r="A15" s="7"/>
       <x:c r="B15" s="7"/>
       <x:c r="C15" s="7"/>
-      <x:c r="D15" s="3"/>
+      <x:c r="D15" s="12"/>
       <x:c r="E15" s="3"/>
       <x:c r="F15" s="3"/>
       <x:c r="G15" s="3"/>
@@ -1239,7 +1290,7 @@
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
-      <x:c r="D19" s="3"/>
+      <x:c r="D19" s="12"/>
       <x:c r="E19" s="3"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
@@ -2292,7 +2343,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -14,93 +14,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Arrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Arrow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Tree_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefab2DObject/SkillObject_Sword_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2D/skill_Sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2D/skill_Sword_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2D/tree-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼 공격 1번째</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
   <x:si>
     <x:t>칼 공격 2번째</x:t>
   </x:si>
   <x:si>
-    <x:t>2D/skill_Sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefab2DObject/SkillObject_Tree_01</x:t>
+    <x:t>SpritePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Tree_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Sword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_Sword_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>칼 공격1</x:t>
   </x:si>
   <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼 공격2</x:t>
+  </x:si>
+  <x:si>
     <x:t>파이어볼</x:t>
   </x:si>
   <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefab2DObject/SkillObject_Sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼 공격2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼 공격 1번째</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_Sword_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2D/tree-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpritePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_Tree_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_Sword_01</x:t>
+    <x:t>화살공격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화살공격1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2D/skill_Arrow_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -987,51 +1008,51 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F3" s="2"/>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="12"/>
       <x:c r="E4" s="3"/>
@@ -1048,13 +1069,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="12"/>
       <x:c r="E5" s="3"/>
@@ -1071,13 +1092,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="12"/>
       <x:c r="E6" s="3"/>
@@ -1094,19 +1115,19 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D7" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="3"/>
       <x:c r="G7" s="3"/>
@@ -1121,19 +1142,19 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="3"/>
       <x:c r="G8" s="3"/>
@@ -1148,16 +1169,20 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="12"/>
-      <x:c r="E9" s="3"/>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F9" s="3"/>
       <x:c r="G9" s="3"/>
       <x:c r="H9" s="3"/>
@@ -1170,11 +1195,21 @@
       <x:c r="O9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="7"/>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7"/>
-      <x:c r="D10" s="12"/>
-      <x:c r="E10" s="3"/>
+      <x:c r="A10" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="F10" s="3"/>
       <x:c r="G10" s="3"/>
       <x:c r="H10" s="3"/>
@@ -2343,7 +2378,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>